--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/107.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/107.xlsx
@@ -426,13 +426,13 @@
         <v>-17.1672989032623</v>
       </c>
       <c r="E2">
-        <v>-13.34868000707168</v>
+        <v>-16.04279599150698</v>
       </c>
       <c r="F2">
-        <v>-3.412334579602248</v>
+        <v>-4.448281741501879</v>
       </c>
       <c r="G2">
-        <v>-7.778535092287318</v>
+        <v>-9.219887030266285</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.61211285695485</v>
       </c>
       <c r="E3">
-        <v>-13.66108131496482</v>
+        <v>-17.06064298031502</v>
       </c>
       <c r="F3">
-        <v>-3.156745130938072</v>
+        <v>-4.572718264383019</v>
       </c>
       <c r="G3">
-        <v>-9.39947750468067</v>
+        <v>-9.560038963335321</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.09816473815481</v>
       </c>
       <c r="E4">
-        <v>-12.90302382302882</v>
+        <v>-16.80164143792032</v>
       </c>
       <c r="F4">
-        <v>-3.455046859625396</v>
+        <v>-4.233054494539109</v>
       </c>
       <c r="G4">
-        <v>-7.542599132794539</v>
+        <v>-9.788082582262479</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.5296608721271</v>
       </c>
       <c r="E5">
-        <v>-13.94619403848775</v>
+        <v>-17.14344159907127</v>
       </c>
       <c r="F5">
-        <v>-3.26194199252179</v>
+        <v>-3.813151744590428</v>
       </c>
       <c r="G5">
-        <v>-7.765749765414653</v>
+        <v>-9.53220389644113</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.86015742523485</v>
       </c>
       <c r="E6">
-        <v>-15.32938925328661</v>
+        <v>-18.73381449972105</v>
       </c>
       <c r="F6">
-        <v>-3.811233245685545</v>
+        <v>-4.232786103500602</v>
       </c>
       <c r="G6">
-        <v>-7.639608048731803</v>
+        <v>-9.453922736619523</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.04660320247283</v>
       </c>
       <c r="E7">
-        <v>-15.97800711387925</v>
+        <v>-18.88152879337725</v>
       </c>
       <c r="F7">
-        <v>-2.921848299995828</v>
+        <v>-4.434034650541131</v>
       </c>
       <c r="G7">
-        <v>-6.834331088486244</v>
+        <v>-10.1631078020422</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-19.06877214655897</v>
       </c>
       <c r="E8">
-        <v>-15.60931687407076</v>
+        <v>-19.09478369134646</v>
       </c>
       <c r="F8">
-        <v>-3.316229050264255</v>
+        <v>-4.114293116734549</v>
       </c>
       <c r="G8">
-        <v>-9.076692693510651</v>
+        <v>-9.081363873266563</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.88971444440134</v>
       </c>
       <c r="E9">
-        <v>-16.94485895688691</v>
+        <v>-19.42115987002728</v>
       </c>
       <c r="F9">
-        <v>-3.049961117410591</v>
+        <v>-3.969202081032007</v>
       </c>
       <c r="G9">
-        <v>-6.075921521440146</v>
+        <v>-8.495989900467091</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.5048624269497</v>
       </c>
       <c r="E10">
-        <v>-19.62159918655479</v>
+        <v>-19.58340150830008</v>
       </c>
       <c r="F10">
-        <v>-3.502615857731158</v>
+        <v>-3.884815465341419</v>
       </c>
       <c r="G10">
-        <v>-6.091530743657811</v>
+        <v>-9.091467658252418</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.9318306467603</v>
       </c>
       <c r="E11">
-        <v>-18.30317926396164</v>
+        <v>-21.11251774104811</v>
       </c>
       <c r="F11">
-        <v>-3.178913899371793</v>
+        <v>-3.806829644572263</v>
       </c>
       <c r="G11">
-        <v>-6.61617606908489</v>
+        <v>-9.321027507036559</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-17.18135179520664</v>
       </c>
       <c r="E12">
-        <v>-18.65160911105981</v>
+        <v>-20.81403696225454</v>
       </c>
       <c r="F12">
-        <v>-3.082283185100425</v>
+        <v>-4.016168856035934</v>
       </c>
       <c r="G12">
-        <v>-6.885853108713921</v>
+        <v>-8.608700733897118</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.28237531994736</v>
       </c>
       <c r="E13">
-        <v>-18.72385638537818</v>
+        <v>-21.14729189295301</v>
       </c>
       <c r="F13">
-        <v>-3.036596237733824</v>
+        <v>-3.688148618405775</v>
       </c>
       <c r="G13">
-        <v>-6.199527360239915</v>
+        <v>-8.655223830360496</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.29611681280203</v>
       </c>
       <c r="E14">
-        <v>-20.23282090879207</v>
+        <v>-22.36928249002683</v>
       </c>
       <c r="F14">
-        <v>-3.127310752014397</v>
+        <v>-3.480160474176069</v>
       </c>
       <c r="G14">
-        <v>-5.175784189312311</v>
+        <v>-6.890203165552523</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.26388285103523</v>
       </c>
       <c r="E15">
-        <v>-20.60955371843819</v>
+        <v>-23.45927712672507</v>
       </c>
       <c r="F15">
-        <v>-2.703484854046058</v>
+        <v>-3.585046697983737</v>
       </c>
       <c r="G15">
-        <v>-5.177300419169297</v>
+        <v>-7.028428373453713</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.23289722111556</v>
       </c>
       <c r="E16">
-        <v>-19.77483369002633</v>
+        <v>-23.11012725225968</v>
       </c>
       <c r="F16">
-        <v>-2.19817493976654</v>
+        <v>-3.331977142958877</v>
       </c>
       <c r="G16">
-        <v>-4.42938528148269</v>
+        <v>-6.080579459013902</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.27093071544982</v>
       </c>
       <c r="E17">
-        <v>-22.66815724605906</v>
+        <v>-25.07616877116377</v>
       </c>
       <c r="F17">
-        <v>-1.930678538054524</v>
+        <v>-3.106224659776136</v>
       </c>
       <c r="G17">
-        <v>-3.198256295792981</v>
+        <v>-6.266218300128533</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.41813391495544</v>
       </c>
       <c r="E18">
-        <v>-25.67698858860544</v>
+        <v>-25.3740382059663</v>
       </c>
       <c r="F18">
-        <v>-2.37689106508352</v>
+        <v>-2.968036409641122</v>
       </c>
       <c r="G18">
-        <v>-4.658484964436874</v>
+        <v>-6.140480470001474</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.70146314501683</v>
       </c>
       <c r="E19">
-        <v>-25.23431214045963</v>
+        <v>-25.58143325856959</v>
       </c>
       <c r="F19">
-        <v>-2.188990002004299</v>
+        <v>-3.196080985427409</v>
       </c>
       <c r="G19">
-        <v>-4.179770147821642</v>
+        <v>-6.269803620947564</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.15656246240121</v>
       </c>
       <c r="E20">
-        <v>-23.80810095106191</v>
+        <v>-26.35469736622335</v>
       </c>
       <c r="F20">
-        <v>-2.28011787161887</v>
+        <v>-2.600814513040879</v>
       </c>
       <c r="G20">
-        <v>-4.870253941492973</v>
+        <v>-6.196173777608633</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.788698763749714</v>
       </c>
       <c r="E21">
-        <v>-26.2704179364666</v>
+        <v>-27.78963039655985</v>
       </c>
       <c r="F21">
-        <v>-2.129480916154586</v>
+        <v>-2.368960275569117</v>
       </c>
       <c r="G21">
-        <v>-4.032411144777603</v>
+        <v>-5.877609912001184</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.583340110838364</v>
       </c>
       <c r="E22">
-        <v>-25.53791009488187</v>
+        <v>-27.78388829151812</v>
       </c>
       <c r="F22">
-        <v>-2.183076287115714</v>
+        <v>-1.969387318419942</v>
       </c>
       <c r="G22">
-        <v>-3.467575796503771</v>
+        <v>-5.599027504871515</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.53620031167193</v>
       </c>
       <c r="E23">
-        <v>-26.89466807842395</v>
+        <v>-28.18093130708863</v>
       </c>
       <c r="F23">
-        <v>-1.828702368932891</v>
+        <v>-1.741025477918383</v>
       </c>
       <c r="G23">
-        <v>-2.687359665990495</v>
+        <v>-6.394445660501124</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.624731087026413</v>
       </c>
       <c r="E24">
-        <v>-27.91097085759537</v>
+        <v>-29.08893563036662</v>
       </c>
       <c r="F24">
-        <v>-0.816222027187167</v>
+        <v>-1.785097937216928</v>
       </c>
       <c r="G24">
-        <v>-3.507166610607915</v>
+        <v>-5.428994575429007</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.806881901440658</v>
       </c>
       <c r="E25">
-        <v>-27.69950470685919</v>
+        <v>-28.90365311634278</v>
       </c>
       <c r="F25">
-        <v>-1.208872317951147</v>
+        <v>-1.786078724221842</v>
       </c>
       <c r="G25">
-        <v>-3.222721227328196</v>
+        <v>-6.541556372629718</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.05478397817687</v>
       </c>
       <c r="E26">
-        <v>-27.03745992083381</v>
+        <v>-29.40205243715298</v>
       </c>
       <c r="F26">
-        <v>-1.051034364654326</v>
+        <v>-1.531011975388832</v>
       </c>
       <c r="G26">
-        <v>-4.190612184462755</v>
+        <v>-5.332326645682288</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.3397507319004</v>
       </c>
       <c r="E27">
-        <v>-28.58850302472698</v>
+        <v>-29.96430097723432</v>
       </c>
       <c r="F27">
-        <v>-0.7173754301133104</v>
+        <v>-1.890066997764875</v>
       </c>
       <c r="G27">
-        <v>-4.915995749209083</v>
+        <v>-5.13404152060764</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.62167455855813</v>
       </c>
       <c r="E28">
-        <v>-27.45484031317278</v>
+        <v>-29.48966482377937</v>
       </c>
       <c r="F28">
-        <v>-0.3650152730866931</v>
+        <v>-2.118718766857414</v>
       </c>
       <c r="G28">
-        <v>-3.616172943579498</v>
+        <v>-6.377267239697845</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.8830639301595</v>
       </c>
       <c r="E29">
-        <v>-28.98556868266753</v>
+        <v>-28.88086583513619</v>
       </c>
       <c r="F29">
-        <v>-1.357193986524607</v>
+        <v>-1.652259283769193</v>
       </c>
       <c r="G29">
-        <v>-3.821559188835882</v>
+        <v>-6.252072339039227</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.11726327980744</v>
       </c>
       <c r="E30">
-        <v>-28.10918669338511</v>
+        <v>-29.44521105868308</v>
       </c>
       <c r="F30">
-        <v>-0.6328239693095649</v>
+        <v>-1.660024399803036</v>
       </c>
       <c r="G30">
-        <v>-3.369590269632423</v>
+        <v>-5.802794893359195</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.30730232929262</v>
       </c>
       <c r="E31">
-        <v>-27.06302315660712</v>
+        <v>-30.28918955220362</v>
       </c>
       <c r="F31">
-        <v>-0.929907997914774</v>
+        <v>-1.786236942395777</v>
       </c>
       <c r="G31">
-        <v>-4.009929230020413</v>
+        <v>-6.491706177899372</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.45737792394067</v>
       </c>
       <c r="E32">
-        <v>-26.53262563845873</v>
+        <v>-29.51913160414729</v>
       </c>
       <c r="F32">
-        <v>-0.7741774112906753</v>
+        <v>-1.756411574057981</v>
       </c>
       <c r="G32">
-        <v>-4.029812366529275</v>
+        <v>-6.071144404226978</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.58439700959353</v>
       </c>
       <c r="E33">
-        <v>-28.35275519636167</v>
+        <v>-29.6283040555242</v>
       </c>
       <c r="F33">
-        <v>-1.137712244581058</v>
+        <v>-1.666494777586303</v>
       </c>
       <c r="G33">
-        <v>-3.723010869222858</v>
+        <v>-5.402295025654785</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.68582186478084</v>
       </c>
       <c r="E34">
-        <v>-25.92743131512564</v>
+        <v>-28.13256267621271</v>
       </c>
       <c r="F34">
-        <v>-1.027070524058739</v>
+        <v>-1.604886608737895</v>
       </c>
       <c r="G34">
-        <v>-3.540619673282251</v>
+        <v>-5.218801418049601</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.77055526627864</v>
       </c>
       <c r="E35">
-        <v>-26.92629494089352</v>
+        <v>-28.40031323039022</v>
       </c>
       <c r="F35">
-        <v>-0.4320310243405759</v>
+        <v>-1.656546913446084</v>
       </c>
       <c r="G35">
-        <v>-4.949809661347199</v>
+        <v>-6.750266405607531</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.85430097421502</v>
       </c>
       <c r="E36">
-        <v>-23.92523445974431</v>
+        <v>-28.27259214947789</v>
       </c>
       <c r="F36">
-        <v>-0.8455876516164095</v>
+        <v>-1.879993221779431</v>
       </c>
       <c r="G36">
-        <v>-5.023509026142454</v>
+        <v>-6.306835383349851</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.93223100930606</v>
       </c>
       <c r="E37">
-        <v>-26.41569138263266</v>
+        <v>-28.21598622438201</v>
       </c>
       <c r="F37">
-        <v>-1.487566590214207</v>
+        <v>-1.968396591006194</v>
       </c>
       <c r="G37">
-        <v>-5.570464117958682</v>
+        <v>-6.509414285988933</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.00201160354749</v>
       </c>
       <c r="E38">
-        <v>-24.06748741374726</v>
+        <v>-26.92777122342002</v>
       </c>
       <c r="F38">
-        <v>-0.6947899928759819</v>
+        <v>-1.767346852142337</v>
       </c>
       <c r="G38">
-        <v>-4.494533507150008</v>
+        <v>-6.009886069568305</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.07065272327377</v>
       </c>
       <c r="E39">
-        <v>-24.68233191519069</v>
+        <v>-26.22399654941397</v>
       </c>
       <c r="F39">
-        <v>-0.3532963594392885</v>
+        <v>-1.603511518849248</v>
       </c>
       <c r="G39">
-        <v>-4.782882023620528</v>
+        <v>-5.84556383118104</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.12830069631487</v>
       </c>
       <c r="E40">
-        <v>-24.02408199038374</v>
+        <v>-26.27373277944021</v>
       </c>
       <c r="F40">
-        <v>-1.229811789159112</v>
+        <v>-1.606869720300197</v>
       </c>
       <c r="G40">
-        <v>-3.38177638776248</v>
+        <v>-6.53922905911561</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.16297819436682</v>
       </c>
       <c r="E41">
-        <v>-22.66011920469545</v>
+        <v>-25.85001252349051</v>
       </c>
       <c r="F41">
-        <v>-0.904039740660151</v>
+        <v>-1.629997738186359</v>
       </c>
       <c r="G41">
-        <v>-3.585924488987177</v>
+        <v>-6.214855186086741</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.1779015511868</v>
       </c>
       <c r="E42">
-        <v>-22.50068974878141</v>
+        <v>-25.21531066352345</v>
       </c>
       <c r="F42">
-        <v>-0.7580822326542809</v>
+        <v>-2.081150648405651</v>
       </c>
       <c r="G42">
-        <v>-3.691448128051446</v>
+        <v>-6.109089877198104</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.16761665449663</v>
       </c>
       <c r="E43">
-        <v>-22.21679971324055</v>
+        <v>-26.89545603290129</v>
       </c>
       <c r="F43">
-        <v>-0.5317921390271232</v>
+        <v>-1.351396243072413</v>
       </c>
       <c r="G43">
-        <v>-3.596779767810447</v>
+        <v>-5.958284596247684</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.12204802899339</v>
       </c>
       <c r="E44">
-        <v>-22.1127444374923</v>
+        <v>-23.21917290636438</v>
       </c>
       <c r="F44">
-        <v>-1.127195292035115</v>
+        <v>-1.767896888097796</v>
       </c>
       <c r="G44">
-        <v>-5.523159732748037</v>
+        <v>-6.116591573390093</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.04932614151799</v>
       </c>
       <c r="E45">
-        <v>-20.4605488096898</v>
+        <v>-23.10401381234932</v>
       </c>
       <c r="F45">
-        <v>-0.5820450475179552</v>
+        <v>-1.857749071912056</v>
       </c>
       <c r="G45">
-        <v>-4.381746531172578</v>
+        <v>-5.943248098408315</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.95627371323617</v>
       </c>
       <c r="E46">
-        <v>-21.0777934023573</v>
+        <v>-23.52233159880787</v>
       </c>
       <c r="F46">
-        <v>-0.7856884047199773</v>
+        <v>-1.551647435759971</v>
       </c>
       <c r="G46">
-        <v>-4.335110876160864</v>
+        <v>-5.742228462718229</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.83958658559593</v>
       </c>
       <c r="E47">
-        <v>-21.38049471892601</v>
+        <v>-22.61477559445665</v>
       </c>
       <c r="F47">
-        <v>-0.5589277984080294</v>
+        <v>-1.301449002153214</v>
       </c>
       <c r="G47">
-        <v>-4.28680008510628</v>
+        <v>-6.110311468502096</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.71220409475778</v>
       </c>
       <c r="E48">
-        <v>-19.31559661243448</v>
+        <v>-22.09763291972871</v>
       </c>
       <c r="F48">
-        <v>-0.4678645414508769</v>
+        <v>-1.648655057199613</v>
       </c>
       <c r="G48">
-        <v>-3.746727617466196</v>
+        <v>-6.838303743133369</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.58910768142277</v>
       </c>
       <c r="E49">
-        <v>-18.5340001126066</v>
+        <v>-22.20075080135737</v>
       </c>
       <c r="F49">
-        <v>-0.5536875462179197</v>
+        <v>-1.608708695934412</v>
       </c>
       <c r="G49">
-        <v>-4.049000288474891</v>
+        <v>-5.513002979033553</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.46769830931256</v>
       </c>
       <c r="E50">
-        <v>-18.32197243109347</v>
+        <v>-21.17938518824537</v>
       </c>
       <c r="F50">
-        <v>-1.361449309872788</v>
+        <v>-1.639356633103188</v>
       </c>
       <c r="G50">
-        <v>-4.224475754783961</v>
+        <v>-6.316644529782712</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.35665258693771</v>
       </c>
       <c r="E51">
-        <v>-17.63719470554959</v>
+        <v>-20.37377871922883</v>
       </c>
       <c r="F51">
-        <v>-0.5721120939909863</v>
+        <v>-1.572620870031452</v>
       </c>
       <c r="G51">
-        <v>-3.878080132827859</v>
+        <v>-6.041207140915349</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.27088786251753</v>
       </c>
       <c r="E52">
-        <v>-17.71511615779957</v>
+        <v>-19.55333244088915</v>
       </c>
       <c r="F52">
-        <v>-0.738113608042396</v>
+        <v>-1.662288327914887</v>
       </c>
       <c r="G52">
-        <v>-5.428382124504242</v>
+        <v>-6.138603390680707</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.20189054834718</v>
       </c>
       <c r="E53">
-        <v>-17.22554283283033</v>
+        <v>-18.57824783213555</v>
       </c>
       <c r="F53">
-        <v>-0.9114552856500122</v>
+        <v>-1.437837209921944</v>
       </c>
       <c r="G53">
-        <v>-4.219552973567064</v>
+        <v>-6.46714192999798</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.1496882628232</v>
       </c>
       <c r="E54">
-        <v>-16.74805600498756</v>
+        <v>-18.99573237937669</v>
       </c>
       <c r="F54">
-        <v>-0.9262126509308853</v>
+        <v>-1.437826441145708</v>
       </c>
       <c r="G54">
-        <v>-4.906885127885009</v>
+        <v>-7.098651665432734</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.12480459625459</v>
       </c>
       <c r="E55">
-        <v>-15.56357022964527</v>
+        <v>-18.89030044753011</v>
       </c>
       <c r="F55">
-        <v>-0.530107239729829</v>
+        <v>-1.685469361314828</v>
       </c>
       <c r="G55">
-        <v>-5.356341343024162</v>
+        <v>-6.360651611636244</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.11461996920922</v>
       </c>
       <c r="E56">
-        <v>-14.32318949962631</v>
+        <v>-18.59333670752911</v>
       </c>
       <c r="F56">
-        <v>-1.029095053991181</v>
+        <v>-1.600721577436619</v>
       </c>
       <c r="G56">
-        <v>-3.877533892813879</v>
+        <v>-6.455045196597483</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.11176853131209</v>
       </c>
       <c r="E57">
-        <v>-14.75863850325587</v>
+        <v>-17.42463266410355</v>
       </c>
       <c r="F57">
-        <v>-1.046794780286798</v>
+        <v>-1.616110158678426</v>
       </c>
       <c r="G57">
-        <v>-4.45005301728436</v>
+        <v>-6.6994395999431</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.12146318318153</v>
       </c>
       <c r="E58">
-        <v>-15.45115991935287</v>
+        <v>-17.48646444820428</v>
       </c>
       <c r="F58">
-        <v>0.05659474207915727</v>
+        <v>-1.378961825135372</v>
       </c>
       <c r="G58">
-        <v>-4.698386969821709</v>
+        <v>-6.984580197786067</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.13212586464646</v>
       </c>
       <c r="E59">
-        <v>-14.52255103933999</v>
+        <v>-17.28310426594183</v>
       </c>
       <c r="F59">
-        <v>-1.045647491433921</v>
+        <v>-1.233850908615163</v>
       </c>
       <c r="G59">
-        <v>-5.15948306307694</v>
+        <v>-6.705100632815253</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.132750792407</v>
       </c>
       <c r="E60">
-        <v>-11.51400499065609</v>
+        <v>-16.24367909848724</v>
       </c>
       <c r="F60">
-        <v>-0.7755152246461965</v>
+        <v>-1.484470152862542</v>
       </c>
       <c r="G60">
-        <v>-5.370685936845824</v>
+        <v>-6.71351935012162</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.12680673924756</v>
       </c>
       <c r="E61">
-        <v>-14.18646581238672</v>
+        <v>-16.01060306978646</v>
       </c>
       <c r="F61">
-        <v>-0.2849875266696357</v>
+        <v>-1.481827660847612</v>
       </c>
       <c r="G61">
-        <v>-5.114105415370149</v>
+        <v>-6.700790302523123</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.10672355478155</v>
       </c>
       <c r="E62">
-        <v>-11.82483944654259</v>
+        <v>-15.97608251242599</v>
       </c>
       <c r="F62">
-        <v>-0.5593345268028039</v>
+        <v>-1.696742613299527</v>
       </c>
       <c r="G62">
-        <v>-6.332435832005036</v>
+        <v>-7.383421482175302</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.06077157055928</v>
       </c>
       <c r="E63">
-        <v>-13.37442438180528</v>
+        <v>-16.73245541203114</v>
       </c>
       <c r="F63">
-        <v>-1.231602719483965</v>
+        <v>-1.458487580906333</v>
       </c>
       <c r="G63">
-        <v>-5.860861862118012</v>
+        <v>-7.540291682553668</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.99230518033293</v>
       </c>
       <c r="E64">
-        <v>-12.77384910196002</v>
+        <v>-14.99000729725577</v>
       </c>
       <c r="F64">
-        <v>-1.106472853086683</v>
+        <v>-1.688596448260396</v>
       </c>
       <c r="G64">
-        <v>-6.04211423039311</v>
+        <v>-7.429328817168376</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.90012670403394</v>
       </c>
       <c r="E65">
-        <v>-12.68121010918511</v>
+        <v>-15.14869408343255</v>
       </c>
       <c r="F65">
-        <v>-0.5168533612850369</v>
+        <v>-2.373221397489118</v>
       </c>
       <c r="G65">
-        <v>-4.598713064725333</v>
+        <v>-7.48640924335649</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.77525018038391</v>
       </c>
       <c r="E66">
-        <v>-12.59832544942272</v>
+        <v>-15.22815974531915</v>
       </c>
       <c r="F66">
-        <v>-0.518558969767401</v>
+        <v>-1.538117710970047</v>
       </c>
       <c r="G66">
-        <v>-6.00963115756178</v>
+        <v>-7.053125043176676</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.62284302218094</v>
       </c>
       <c r="E67">
-        <v>-11.75564889217939</v>
+        <v>-14.86938233511345</v>
       </c>
       <c r="F67">
-        <v>-0.7704257353233963</v>
+        <v>-1.971772188172602</v>
       </c>
       <c r="G67">
-        <v>-5.523699351670938</v>
+        <v>-8.355917408154989</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.4499618758527</v>
       </c>
       <c r="E68">
-        <v>-12.8175805754521</v>
+        <v>-14.37177096878059</v>
       </c>
       <c r="F68">
-        <v>-1.383302470326041</v>
+        <v>-1.775830162714407</v>
       </c>
       <c r="G68">
-        <v>-5.922497598968163</v>
+        <v>-7.63430786532343</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.25242651489687</v>
       </c>
       <c r="E69">
-        <v>-12.66690465979488</v>
+        <v>-13.93675217018176</v>
       </c>
       <c r="F69">
-        <v>-0.9820189344900853</v>
+        <v>-1.722514779935425</v>
       </c>
       <c r="G69">
-        <v>-5.028378838630722</v>
+        <v>-7.597276102921143</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.03707974868634</v>
       </c>
       <c r="E70">
-        <v>-11.85049325179604</v>
+        <v>-13.70438258342617</v>
       </c>
       <c r="F70">
-        <v>-0.9952405066061681</v>
+        <v>-1.550830665500811</v>
       </c>
       <c r="G70">
-        <v>-6.284247531135404</v>
+        <v>-8.288892103166903</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.816853009733643</v>
       </c>
       <c r="E71">
-        <v>-11.24229655019587</v>
+        <v>-14.46018489530635</v>
       </c>
       <c r="F71">
-        <v>-0.7178393158588782</v>
+        <v>-2.234097920556344</v>
       </c>
       <c r="G71">
-        <v>-5.523702662216477</v>
+        <v>-8.274878563899168</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.588107668150679</v>
       </c>
       <c r="E72">
-        <v>-9.899667405557716</v>
+        <v>-14.63355752269001</v>
       </c>
       <c r="F72">
-        <v>-0.9680700557943444</v>
+        <v>-1.506420232301924</v>
       </c>
       <c r="G72">
-        <v>-5.842624066742167</v>
+        <v>-8.531915940659262</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.352904393151698</v>
       </c>
       <c r="E73">
-        <v>-11.89575987797671</v>
+        <v>-15.67272456712616</v>
       </c>
       <c r="F73">
-        <v>-1.290234564254114</v>
+        <v>-1.660257171043223</v>
       </c>
       <c r="G73">
-        <v>-5.199487695373493</v>
+        <v>-7.586576419738218</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.123798242251253</v>
       </c>
       <c r="E74">
-        <v>-12.04964195323136</v>
+        <v>-13.88141421780802</v>
       </c>
       <c r="F74">
-        <v>-1.264807826825183</v>
+        <v>-2.265206430001076</v>
       </c>
       <c r="G74">
-        <v>-6.336067500461616</v>
+        <v>-7.665417061755961</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.89503628261531</v>
       </c>
       <c r="E75">
-        <v>-14.4518298607622</v>
+        <v>-14.39969353951189</v>
       </c>
       <c r="F75">
-        <v>-1.130680233698693</v>
+        <v>-2.064895594860517</v>
       </c>
       <c r="G75">
-        <v>-5.181246589452108</v>
+        <v>-7.351772666819869</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.664524195814787</v>
       </c>
       <c r="E76">
-        <v>-12.87324910642839</v>
+        <v>-15.3757245993331</v>
       </c>
       <c r="F76">
-        <v>-1.105680105482204</v>
+        <v>-2.212012817230306</v>
       </c>
       <c r="G76">
-        <v>-5.869740745254338</v>
+        <v>-8.290868498853849</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.441978879854592</v>
       </c>
       <c r="E77">
-        <v>-11.85244502409334</v>
+        <v>-15.51177807241955</v>
       </c>
       <c r="F77">
-        <v>-1.897515677450848</v>
+        <v>-2.71072312841172</v>
       </c>
       <c r="G77">
-        <v>-4.350468496917543</v>
+        <v>-7.324765236310495</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.222901906587577</v>
       </c>
       <c r="E78">
-        <v>-12.93839573350273</v>
+        <v>-15.63129355842998</v>
       </c>
       <c r="F78">
-        <v>-2.297728134234985</v>
+        <v>-2.442619533393452</v>
       </c>
       <c r="G78">
-        <v>-5.545565504957824</v>
+        <v>-7.532309957258485</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.003003875316523</v>
       </c>
       <c r="E79">
-        <v>-14.1461895645625</v>
+        <v>-15.37039458542607</v>
       </c>
       <c r="F79">
-        <v>-1.447102499322257</v>
+        <v>-2.454520687869473</v>
       </c>
       <c r="G79">
-        <v>-5.595779859697489</v>
+        <v>-7.258458319704433</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.790183039793956</v>
       </c>
       <c r="E80">
-        <v>-13.78970356220468</v>
+        <v>-16.38561958778366</v>
       </c>
       <c r="F80">
-        <v>-1.91958421342883</v>
+        <v>-2.585700949776802</v>
       </c>
       <c r="G80">
-        <v>-5.03951551382483</v>
+        <v>-7.001818208409052</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.582633535039331</v>
       </c>
       <c r="E81">
-        <v>-14.35386085408026</v>
+        <v>-17.10761684119658</v>
       </c>
       <c r="F81">
-        <v>-2.124666444809515</v>
+        <v>-2.527282823796575</v>
       </c>
       <c r="G81">
-        <v>-4.70524642017908</v>
+        <v>-6.603072929840455</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.375751513708465</v>
       </c>
       <c r="E82">
-        <v>-14.98560562052031</v>
+        <v>-17.63291982608635</v>
       </c>
       <c r="F82">
-        <v>-1.822394351160572</v>
+        <v>-2.66439419630795</v>
       </c>
       <c r="G82">
-        <v>-5.354282183698735</v>
+        <v>-7.395577805395506</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.17733955400268</v>
       </c>
       <c r="E83">
-        <v>-16.38265343730864</v>
+        <v>-18.69601985565303</v>
       </c>
       <c r="F83">
-        <v>-2.571119198385322</v>
+        <v>-2.8921024549287</v>
       </c>
       <c r="G83">
-        <v>-4.472468721130765</v>
+        <v>-6.852598678771942</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.990621057441546</v>
       </c>
       <c r="E84">
-        <v>-16.96134260227483</v>
+        <v>-19.48448605055054</v>
       </c>
       <c r="F84">
-        <v>-2.002488051468407</v>
+        <v>-2.837658007379702</v>
       </c>
       <c r="G84">
-        <v>-5.121719670110473</v>
+        <v>-6.168133456891006</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.813382395308884</v>
       </c>
       <c r="E85">
-        <v>-17.7721024747121</v>
+        <v>-20.08595343977531</v>
       </c>
       <c r="F85">
-        <v>-1.753367323852693</v>
+        <v>-2.841307794156437</v>
       </c>
       <c r="G85">
-        <v>-3.18050184006587</v>
+        <v>-7.202040002624173</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.655584367420016</v>
       </c>
       <c r="E86">
-        <v>-19.54391774342721</v>
+        <v>-20.66284480056045</v>
       </c>
       <c r="F86">
-        <v>-2.241958298841508</v>
+        <v>-3.196516706681282</v>
       </c>
       <c r="G86">
-        <v>-5.850880567317109</v>
+        <v>-6.60868099398398</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.526482606469034</v>
       </c>
       <c r="E87">
-        <v>-20.32003931817981</v>
+        <v>-22.16957225781456</v>
       </c>
       <c r="F87">
-        <v>-2.830205185856715</v>
+        <v>-3.17681233127089</v>
       </c>
       <c r="G87">
-        <v>-4.675570689965053</v>
+        <v>-6.6921729524844</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.426331394178331</v>
       </c>
       <c r="E88">
-        <v>-19.91433786030663</v>
+        <v>-21.73757395137884</v>
       </c>
       <c r="F88">
-        <v>-2.802275122136524</v>
+        <v>-3.635716275278177</v>
       </c>
       <c r="G88">
-        <v>-3.08842894752766</v>
+        <v>-6.532697352766628</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.366608923740056</v>
       </c>
       <c r="E89">
-        <v>-22.30306261461266</v>
+        <v>-24.31374583028437</v>
       </c>
       <c r="F89">
-        <v>-2.750602391917294</v>
+        <v>-3.717357681395888</v>
       </c>
       <c r="G89">
-        <v>-3.832434330932388</v>
+        <v>-6.662162857170906</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.360570780828641</v>
       </c>
       <c r="E90">
-        <v>-24.3945247496332</v>
+        <v>-24.7650535498888</v>
       </c>
       <c r="F90">
-        <v>-3.154043824837543</v>
+        <v>-3.727954157212499</v>
       </c>
       <c r="G90">
-        <v>-6.087548157374068</v>
+        <v>-6.85633297414024</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.407444674394526</v>
       </c>
       <c r="E91">
-        <v>-27.33946385240535</v>
+        <v>-26.30907299059607</v>
       </c>
       <c r="F91">
-        <v>-3.786013600107314</v>
+        <v>-3.596836851227782</v>
       </c>
       <c r="G91">
-        <v>-5.679189054559427</v>
+        <v>-6.882264477349351</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.51532083636505</v>
       </c>
       <c r="E92">
-        <v>-26.52925192532301</v>
+        <v>-27.96024518327284</v>
       </c>
       <c r="F92">
-        <v>-3.453133330924929</v>
+        <v>-4.154549287408397</v>
       </c>
       <c r="G92">
-        <v>-6.587387565075388</v>
+        <v>-7.554417780369738</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.694977994811066</v>
       </c>
       <c r="E93">
-        <v>-29.30599897497628</v>
+        <v>-29.52618243817723</v>
       </c>
       <c r="F93">
-        <v>-3.243959792941818</v>
+        <v>-3.889060019913364</v>
       </c>
       <c r="G93">
-        <v>-6.023730771013536</v>
+        <v>-7.808227375229041</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.936728952947645</v>
       </c>
       <c r="E94">
-        <v>-30.55630838425706</v>
+        <v>-31.01911842784098</v>
       </c>
       <c r="F94">
-        <v>-3.068032780670065</v>
+        <v>-4.230292717618175</v>
       </c>
       <c r="G94">
-        <v>-6.312916855505493</v>
+        <v>-7.673587488146882</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.237997238012447</v>
       </c>
       <c r="E95">
-        <v>-32.60246540106786</v>
+        <v>-32.9040028998166</v>
       </c>
       <c r="F95">
-        <v>-3.036631029164741</v>
+        <v>-4.539404640912033</v>
       </c>
       <c r="G95">
-        <v>-6.956758373074032</v>
+        <v>-7.467999299612602</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.60220258865106</v>
       </c>
       <c r="E96">
-        <v>-33.85339747552469</v>
+        <v>-35.11480391036127</v>
       </c>
       <c r="F96">
-        <v>-3.473396854332211</v>
+        <v>-4.682682380369847</v>
       </c>
       <c r="G96">
-        <v>-5.830547196614906</v>
+        <v>-8.093460668347108</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.007150966994061</v>
       </c>
       <c r="E97">
-        <v>-34.59165195062516</v>
+        <v>-36.17011270039776</v>
       </c>
       <c r="F97">
-        <v>-3.673798809887079</v>
+        <v>-4.81162356518741</v>
       </c>
       <c r="G97">
-        <v>-6.507424648119832</v>
+        <v>-8.087806256566033</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.447617617357885</v>
       </c>
       <c r="E98">
-        <v>-38.67796122771257</v>
+        <v>-39.03054594971278</v>
       </c>
       <c r="F98">
-        <v>-3.924222559427397</v>
+        <v>-4.663335859677464</v>
       </c>
       <c r="G98">
-        <v>-6.130850093027735</v>
+        <v>-8.398302322694278</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.90133253254079</v>
       </c>
       <c r="E99">
-        <v>-41.3465819034847</v>
+        <v>-41.34681285565909</v>
       </c>
       <c r="F99">
-        <v>-4.266837802327482</v>
+        <v>-4.90786163330985</v>
       </c>
       <c r="G99">
-        <v>-7.292782055855596</v>
+        <v>-8.718220201427288</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.366719716999585</v>
       </c>
       <c r="E100">
-        <v>-42.94727746063496</v>
+        <v>-42.50262659782181</v>
       </c>
       <c r="F100">
-        <v>-4.132632342665127</v>
+        <v>-5.179274556102303</v>
       </c>
       <c r="G100">
-        <v>-7.096430289375883</v>
+        <v>-8.793131225889915</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.789034092280668</v>
       </c>
       <c r="E101">
-        <v>-46.28872748328173</v>
+        <v>-43.95560786131588</v>
       </c>
       <c r="F101">
-        <v>-4.15015314160174</v>
+        <v>-5.018891858144082</v>
       </c>
       <c r="G101">
-        <v>-5.91747219083955</v>
+        <v>-9.488888718605306</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.21488567825303</v>
       </c>
       <c r="E102">
-        <v>-47.03849333930969</v>
+        <v>-46.89277157421687</v>
       </c>
       <c r="F102">
-        <v>-4.238393322450152</v>
+        <v>-5.168312770261057</v>
       </c>
       <c r="G102">
-        <v>-6.596302864212645</v>
+        <v>-8.346406210820662</v>
       </c>
     </row>
   </sheetData>
